--- a/frontend/public/dap_an.xlsx
+++ b/frontend/public/dap_an.xlsx
@@ -164,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -210,10 +210,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -783,36 +779,16 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
@@ -1308,120 +1284,120 @@
       <c r="F5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
       <c r="AE5" s="11"/>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="12"/>
-      <c r="AM5" s="12"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
-      <c r="AX5" s="12"/>
-      <c r="AY5" s="12"/>
-      <c r="AZ5" s="12"/>
-      <c r="BA5" s="12"/>
-      <c r="BB5" s="12"/>
-      <c r="BC5" s="12"/>
-      <c r="BD5" s="12"/>
-      <c r="BE5" s="12"/>
-      <c r="BF5" s="12"/>
-      <c r="BG5" s="12"/>
-      <c r="BH5" s="12"/>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="10"/>
+      <c r="AM5" s="10"/>
+      <c r="AN5" s="10"/>
+      <c r="AO5" s="10"/>
+      <c r="AP5" s="10"/>
+      <c r="AQ5" s="10"/>
+      <c r="AR5" s="10"/>
+      <c r="AS5" s="10"/>
+      <c r="AT5" s="10"/>
+      <c r="AU5" s="10"/>
+      <c r="AV5" s="10"/>
+      <c r="AW5" s="10"/>
+      <c r="AX5" s="10"/>
+      <c r="AY5" s="10"/>
+      <c r="AZ5" s="10"/>
+      <c r="BA5" s="10"/>
+      <c r="BB5" s="10"/>
+      <c r="BC5" s="10"/>
+      <c r="BD5" s="10"/>
+      <c r="BE5" s="10"/>
+      <c r="BF5" s="10"/>
+      <c r="BG5" s="10"/>
+      <c r="BH5" s="10"/>
       <c r="BI5" s="11"/>
-      <c r="BJ5" s="12"/>
-      <c r="BK5" s="12"/>
-      <c r="BL5" s="12"/>
-      <c r="BM5" s="12"/>
-      <c r="BN5" s="12"/>
-      <c r="BO5" s="12"/>
-      <c r="BP5" s="12"/>
-      <c r="BQ5" s="12"/>
-      <c r="BR5" s="12"/>
-      <c r="BS5" s="12"/>
-      <c r="BT5" s="12"/>
-      <c r="BU5" s="12"/>
-      <c r="BV5" s="12"/>
-      <c r="BW5" s="12"/>
-      <c r="BX5" s="12"/>
-      <c r="BY5" s="12"/>
-      <c r="BZ5" s="12"/>
-      <c r="CA5" s="12"/>
-      <c r="CB5" s="12"/>
-      <c r="CC5" s="12"/>
-      <c r="CD5" s="12"/>
-      <c r="CE5" s="12"/>
-      <c r="CF5" s="12"/>
-      <c r="CG5" s="12"/>
-      <c r="CH5" s="12"/>
-      <c r="CI5" s="12"/>
-      <c r="CJ5" s="12"/>
-      <c r="CK5" s="12"/>
-      <c r="CL5" s="12"/>
+      <c r="BJ5" s="10"/>
+      <c r="BK5" s="10"/>
+      <c r="BL5" s="10"/>
+      <c r="BM5" s="10"/>
+      <c r="BN5" s="10"/>
+      <c r="BO5" s="10"/>
+      <c r="BP5" s="10"/>
+      <c r="BQ5" s="10"/>
+      <c r="BR5" s="10"/>
+      <c r="BS5" s="10"/>
+      <c r="BT5" s="10"/>
+      <c r="BU5" s="10"/>
+      <c r="BV5" s="10"/>
+      <c r="BW5" s="10"/>
+      <c r="BX5" s="10"/>
+      <c r="BY5" s="10"/>
+      <c r="BZ5" s="10"/>
+      <c r="CA5" s="10"/>
+      <c r="CB5" s="10"/>
+      <c r="CC5" s="10"/>
+      <c r="CD5" s="10"/>
+      <c r="CE5" s="10"/>
+      <c r="CF5" s="10"/>
+      <c r="CG5" s="10"/>
+      <c r="CH5" s="10"/>
+      <c r="CI5" s="10"/>
+      <c r="CJ5" s="10"/>
+      <c r="CK5" s="10"/>
+      <c r="CL5" s="10"/>
       <c r="CM5" s="11"/>
-      <c r="CN5" s="12"/>
-      <c r="CO5" s="12"/>
-      <c r="CP5" s="12"/>
-      <c r="CQ5" s="12"/>
-      <c r="CR5" s="12"/>
-      <c r="CS5" s="12"/>
-      <c r="CT5" s="12"/>
-      <c r="CU5" s="12"/>
-      <c r="CV5" s="12"/>
-      <c r="CW5" s="12"/>
-      <c r="CX5" s="12"/>
-      <c r="CY5" s="12"/>
-      <c r="CZ5" s="12"/>
-      <c r="DA5" s="12"/>
-      <c r="DB5" s="12"/>
-      <c r="DC5" s="12"/>
-      <c r="DD5" s="12"/>
-      <c r="DE5" s="12"/>
-      <c r="DF5" s="12"/>
-      <c r="DG5" s="12"/>
-      <c r="DH5" s="12"/>
-      <c r="DI5" s="12"/>
-      <c r="DJ5" s="12"/>
-      <c r="DK5" s="12"/>
-      <c r="DL5" s="12"/>
-      <c r="DM5" s="12"/>
-      <c r="DN5" s="12"/>
-      <c r="DO5" s="12"/>
-      <c r="DP5" s="12"/>
+      <c r="CN5" s="10"/>
+      <c r="CO5" s="10"/>
+      <c r="CP5" s="10"/>
+      <c r="CQ5" s="10"/>
+      <c r="CR5" s="10"/>
+      <c r="CS5" s="10"/>
+      <c r="CT5" s="10"/>
+      <c r="CU5" s="10"/>
+      <c r="CV5" s="10"/>
+      <c r="CW5" s="10"/>
+      <c r="CX5" s="10"/>
+      <c r="CY5" s="10"/>
+      <c r="CZ5" s="10"/>
+      <c r="DA5" s="10"/>
+      <c r="DB5" s="10"/>
+      <c r="DC5" s="10"/>
+      <c r="DD5" s="10"/>
+      <c r="DE5" s="10"/>
+      <c r="DF5" s="10"/>
+      <c r="DG5" s="10"/>
+      <c r="DH5" s="10"/>
+      <c r="DI5" s="10"/>
+      <c r="DJ5" s="10"/>
+      <c r="DK5" s="10"/>
+      <c r="DL5" s="10"/>
+      <c r="DM5" s="10"/>
+      <c r="DN5" s="10"/>
+      <c r="DO5" s="10"/>
+      <c r="DP5" s="10"/>
       <c r="DQ5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1443,120 +1419,120 @@
       <c r="F6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="10"/>
+      <c r="AC6" s="10"/>
+      <c r="AD6" s="10"/>
       <c r="AE6" s="11"/>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="12"/>
-      <c r="AM6" s="12"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="12"/>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="12"/>
-      <c r="AS6" s="12"/>
-      <c r="AT6" s="12"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="12"/>
-      <c r="AX6" s="12"/>
-      <c r="AY6" s="12"/>
-      <c r="AZ6" s="12"/>
-      <c r="BA6" s="12"/>
-      <c r="BB6" s="12"/>
-      <c r="BC6" s="12"/>
-      <c r="BD6" s="12"/>
-      <c r="BE6" s="12"/>
-      <c r="BF6" s="12"/>
-      <c r="BG6" s="12"/>
-      <c r="BH6" s="12"/>
+      <c r="AF6" s="10"/>
+      <c r="AG6" s="10"/>
+      <c r="AH6" s="10"/>
+      <c r="AI6" s="10"/>
+      <c r="AJ6" s="10"/>
+      <c r="AK6" s="10"/>
+      <c r="AL6" s="10"/>
+      <c r="AM6" s="10"/>
+      <c r="AN6" s="10"/>
+      <c r="AO6" s="10"/>
+      <c r="AP6" s="10"/>
+      <c r="AQ6" s="10"/>
+      <c r="AR6" s="10"/>
+      <c r="AS6" s="10"/>
+      <c r="AT6" s="10"/>
+      <c r="AU6" s="10"/>
+      <c r="AV6" s="10"/>
+      <c r="AW6" s="10"/>
+      <c r="AX6" s="10"/>
+      <c r="AY6" s="10"/>
+      <c r="AZ6" s="10"/>
+      <c r="BA6" s="10"/>
+      <c r="BB6" s="10"/>
+      <c r="BC6" s="10"/>
+      <c r="BD6" s="10"/>
+      <c r="BE6" s="10"/>
+      <c r="BF6" s="10"/>
+      <c r="BG6" s="10"/>
+      <c r="BH6" s="10"/>
       <c r="BI6" s="11"/>
-      <c r="BJ6" s="12"/>
-      <c r="BK6" s="12"/>
-      <c r="BL6" s="12"/>
-      <c r="BM6" s="12"/>
-      <c r="BN6" s="12"/>
-      <c r="BO6" s="12"/>
-      <c r="BP6" s="12"/>
-      <c r="BQ6" s="12"/>
-      <c r="BR6" s="12"/>
-      <c r="BS6" s="12"/>
-      <c r="BT6" s="12"/>
-      <c r="BU6" s="12"/>
-      <c r="BV6" s="12"/>
-      <c r="BW6" s="12"/>
-      <c r="BX6" s="12"/>
-      <c r="BY6" s="12"/>
-      <c r="BZ6" s="12"/>
-      <c r="CA6" s="12"/>
-      <c r="CB6" s="12"/>
-      <c r="CC6" s="12"/>
-      <c r="CD6" s="12"/>
-      <c r="CE6" s="12"/>
-      <c r="CF6" s="12"/>
-      <c r="CG6" s="12"/>
-      <c r="CH6" s="12"/>
-      <c r="CI6" s="12"/>
-      <c r="CJ6" s="12"/>
-      <c r="CK6" s="12"/>
-      <c r="CL6" s="12"/>
+      <c r="BJ6" s="10"/>
+      <c r="BK6" s="10"/>
+      <c r="BL6" s="10"/>
+      <c r="BM6" s="10"/>
+      <c r="BN6" s="10"/>
+      <c r="BO6" s="10"/>
+      <c r="BP6" s="10"/>
+      <c r="BQ6" s="10"/>
+      <c r="BR6" s="10"/>
+      <c r="BS6" s="10"/>
+      <c r="BT6" s="10"/>
+      <c r="BU6" s="10"/>
+      <c r="BV6" s="10"/>
+      <c r="BW6" s="10"/>
+      <c r="BX6" s="10"/>
+      <c r="BY6" s="10"/>
+      <c r="BZ6" s="10"/>
+      <c r="CA6" s="10"/>
+      <c r="CB6" s="10"/>
+      <c r="CC6" s="10"/>
+      <c r="CD6" s="10"/>
+      <c r="CE6" s="10"/>
+      <c r="CF6" s="10"/>
+      <c r="CG6" s="10"/>
+      <c r="CH6" s="10"/>
+      <c r="CI6" s="10"/>
+      <c r="CJ6" s="10"/>
+      <c r="CK6" s="10"/>
+      <c r="CL6" s="10"/>
       <c r="CM6" s="11"/>
-      <c r="CN6" s="12"/>
-      <c r="CO6" s="12"/>
-      <c r="CP6" s="12"/>
-      <c r="CQ6" s="12"/>
-      <c r="CR6" s="12"/>
-      <c r="CS6" s="12"/>
-      <c r="CT6" s="12"/>
-      <c r="CU6" s="12"/>
-      <c r="CV6" s="12"/>
-      <c r="CW6" s="12"/>
-      <c r="CX6" s="12"/>
-      <c r="CY6" s="12"/>
-      <c r="CZ6" s="12"/>
-      <c r="DA6" s="12"/>
-      <c r="DB6" s="12"/>
-      <c r="DC6" s="12"/>
-      <c r="DD6" s="12"/>
-      <c r="DE6" s="12"/>
-      <c r="DF6" s="12"/>
-      <c r="DG6" s="12"/>
-      <c r="DH6" s="12"/>
-      <c r="DI6" s="12"/>
-      <c r="DJ6" s="12"/>
-      <c r="DK6" s="12"/>
-      <c r="DL6" s="12"/>
-      <c r="DM6" s="12"/>
-      <c r="DN6" s="12"/>
-      <c r="DO6" s="12"/>
-      <c r="DP6" s="12"/>
+      <c r="CN6" s="10"/>
+      <c r="CO6" s="10"/>
+      <c r="CP6" s="10"/>
+      <c r="CQ6" s="10"/>
+      <c r="CR6" s="10"/>
+      <c r="CS6" s="10"/>
+      <c r="CT6" s="10"/>
+      <c r="CU6" s="10"/>
+      <c r="CV6" s="10"/>
+      <c r="CW6" s="10"/>
+      <c r="CX6" s="10"/>
+      <c r="CY6" s="10"/>
+      <c r="CZ6" s="10"/>
+      <c r="DA6" s="10"/>
+      <c r="DB6" s="10"/>
+      <c r="DC6" s="10"/>
+      <c r="DD6" s="10"/>
+      <c r="DE6" s="10"/>
+      <c r="DF6" s="10"/>
+      <c r="DG6" s="10"/>
+      <c r="DH6" s="10"/>
+      <c r="DI6" s="10"/>
+      <c r="DJ6" s="10"/>
+      <c r="DK6" s="10"/>
+      <c r="DL6" s="10"/>
+      <c r="DM6" s="10"/>
+      <c r="DN6" s="10"/>
+      <c r="DO6" s="10"/>
+      <c r="DP6" s="10"/>
       <c r="DQ6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1578,120 +1554,120 @@
       <c r="F7" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="12"/>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
       <c r="AE7" s="11"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12"/>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="12"/>
-      <c r="AQ7" s="12"/>
-      <c r="AR7" s="12"/>
-      <c r="AS7" s="12"/>
-      <c r="AT7" s="12"/>
-      <c r="AU7" s="12"/>
-      <c r="AV7" s="12"/>
-      <c r="AW7" s="12"/>
-      <c r="AX7" s="12"/>
-      <c r="AY7" s="12"/>
-      <c r="AZ7" s="12"/>
-      <c r="BA7" s="12"/>
-      <c r="BB7" s="12"/>
-      <c r="BC7" s="12"/>
-      <c r="BD7" s="12"/>
-      <c r="BE7" s="12"/>
-      <c r="BF7" s="12"/>
-      <c r="BG7" s="12"/>
-      <c r="BH7" s="12"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="10"/>
+      <c r="AK7" s="10"/>
+      <c r="AL7" s="10"/>
+      <c r="AM7" s="10"/>
+      <c r="AN7" s="10"/>
+      <c r="AO7" s="10"/>
+      <c r="AP7" s="10"/>
+      <c r="AQ7" s="10"/>
+      <c r="AR7" s="10"/>
+      <c r="AS7" s="10"/>
+      <c r="AT7" s="10"/>
+      <c r="AU7" s="10"/>
+      <c r="AV7" s="10"/>
+      <c r="AW7" s="10"/>
+      <c r="AX7" s="10"/>
+      <c r="AY7" s="10"/>
+      <c r="AZ7" s="10"/>
+      <c r="BA7" s="10"/>
+      <c r="BB7" s="10"/>
+      <c r="BC7" s="10"/>
+      <c r="BD7" s="10"/>
+      <c r="BE7" s="10"/>
+      <c r="BF7" s="10"/>
+      <c r="BG7" s="10"/>
+      <c r="BH7" s="10"/>
       <c r="BI7" s="11"/>
-      <c r="BJ7" s="12"/>
-      <c r="BK7" s="12"/>
-      <c r="BL7" s="12"/>
-      <c r="BM7" s="12"/>
-      <c r="BN7" s="12"/>
-      <c r="BO7" s="12"/>
-      <c r="BP7" s="12"/>
-      <c r="BQ7" s="12"/>
-      <c r="BR7" s="12"/>
-      <c r="BS7" s="12"/>
-      <c r="BT7" s="12"/>
-      <c r="BU7" s="12"/>
-      <c r="BV7" s="12"/>
-      <c r="BW7" s="12"/>
-      <c r="BX7" s="12"/>
-      <c r="BY7" s="12"/>
-      <c r="BZ7" s="12"/>
-      <c r="CA7" s="12"/>
-      <c r="CB7" s="12"/>
-      <c r="CC7" s="12"/>
-      <c r="CD7" s="12"/>
-      <c r="CE7" s="12"/>
-      <c r="CF7" s="12"/>
-      <c r="CG7" s="12"/>
-      <c r="CH7" s="12"/>
-      <c r="CI7" s="12"/>
-      <c r="CJ7" s="12"/>
-      <c r="CK7" s="12"/>
-      <c r="CL7" s="12"/>
+      <c r="BJ7" s="10"/>
+      <c r="BK7" s="10"/>
+      <c r="BL7" s="10"/>
+      <c r="BM7" s="10"/>
+      <c r="BN7" s="10"/>
+      <c r="BO7" s="10"/>
+      <c r="BP7" s="10"/>
+      <c r="BQ7" s="10"/>
+      <c r="BR7" s="10"/>
+      <c r="BS7" s="10"/>
+      <c r="BT7" s="10"/>
+      <c r="BU7" s="10"/>
+      <c r="BV7" s="10"/>
+      <c r="BW7" s="10"/>
+      <c r="BX7" s="10"/>
+      <c r="BY7" s="10"/>
+      <c r="BZ7" s="10"/>
+      <c r="CA7" s="10"/>
+      <c r="CB7" s="10"/>
+      <c r="CC7" s="10"/>
+      <c r="CD7" s="10"/>
+      <c r="CE7" s="10"/>
+      <c r="CF7" s="10"/>
+      <c r="CG7" s="10"/>
+      <c r="CH7" s="10"/>
+      <c r="CI7" s="10"/>
+      <c r="CJ7" s="10"/>
+      <c r="CK7" s="10"/>
+      <c r="CL7" s="10"/>
       <c r="CM7" s="11"/>
-      <c r="CN7" s="12"/>
-      <c r="CO7" s="12"/>
-      <c r="CP7" s="12"/>
-      <c r="CQ7" s="12"/>
-      <c r="CR7" s="12"/>
-      <c r="CS7" s="12"/>
-      <c r="CT7" s="12"/>
-      <c r="CU7" s="12"/>
-      <c r="CV7" s="12"/>
-      <c r="CW7" s="12"/>
-      <c r="CX7" s="12"/>
-      <c r="CY7" s="12"/>
-      <c r="CZ7" s="12"/>
-      <c r="DA7" s="12"/>
-      <c r="DB7" s="12"/>
-      <c r="DC7" s="12"/>
-      <c r="DD7" s="12"/>
-      <c r="DE7" s="12"/>
-      <c r="DF7" s="12"/>
-      <c r="DG7" s="12"/>
-      <c r="DH7" s="12"/>
-      <c r="DI7" s="12"/>
-      <c r="DJ7" s="12"/>
-      <c r="DK7" s="12"/>
-      <c r="DL7" s="12"/>
-      <c r="DM7" s="12"/>
-      <c r="DN7" s="12"/>
-      <c r="DO7" s="12"/>
-      <c r="DP7" s="12"/>
+      <c r="CN7" s="10"/>
+      <c r="CO7" s="10"/>
+      <c r="CP7" s="10"/>
+      <c r="CQ7" s="10"/>
+      <c r="CR7" s="10"/>
+      <c r="CS7" s="10"/>
+      <c r="CT7" s="10"/>
+      <c r="CU7" s="10"/>
+      <c r="CV7" s="10"/>
+      <c r="CW7" s="10"/>
+      <c r="CX7" s="10"/>
+      <c r="CY7" s="10"/>
+      <c r="CZ7" s="10"/>
+      <c r="DA7" s="10"/>
+      <c r="DB7" s="10"/>
+      <c r="DC7" s="10"/>
+      <c r="DD7" s="10"/>
+      <c r="DE7" s="10"/>
+      <c r="DF7" s="10"/>
+      <c r="DG7" s="10"/>
+      <c r="DH7" s="10"/>
+      <c r="DI7" s="10"/>
+      <c r="DJ7" s="10"/>
+      <c r="DK7" s="10"/>
+      <c r="DL7" s="10"/>
+      <c r="DM7" s="10"/>
+      <c r="DN7" s="10"/>
+      <c r="DO7" s="10"/>
+      <c r="DP7" s="10"/>
       <c r="DQ7" s="11"/>
     </row>
   </sheetData>
